--- a/data/profiling_combine.xlsx
+++ b/data/profiling_combine.xlsx
@@ -5,13 +5,13 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="mesures_combine" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="stations_combine" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="dic_data" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="Feuille4" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="meta_stations" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">dic_data!$A$25:$G$40</definedName>
@@ -1932,7 +1932,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G1048576"/>
+  <dimension ref="A1:G68"/>
   <sheetFormatPr defaultColWidth="10.16015625" defaultRowHeight="13.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="27.03"/>
@@ -1942,7 +1942,7 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="10.16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="23.21"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="18.63"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="9" min="8" style="2" width="10.16"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="10.16"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="13" style="2" width="10.16"/>
   </cols>
   <sheetData>
@@ -3152,98 +3152,6 @@
     <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="22"/>
     </row>
-    <row r="1048485" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048486" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048487" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048488" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048489" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048490" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048491" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048492" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048493" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048494" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048495" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048496" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048497" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048498" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048499" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048500" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048501" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048502" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048503" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048504" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048505" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048506" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048507" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048508" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048509" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048510" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048511" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048512" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048513" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048514" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048515" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048516" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048517" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048518" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048519" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048520" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048521" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048522" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048523" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048524" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048525" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048526" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048527" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048528" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048529" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048530" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048531" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048532" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048533" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048534" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048535" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048536" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048537" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048538" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048539" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048540" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048541" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048542" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048543" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048544" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048545" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048546" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048547" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048548" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048549" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048550" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048551" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048552" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048553" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048554" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048555" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048556" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048557" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048558" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048559" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048560" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048561" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048562" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048563" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048564" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048565" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048566" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048567" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048568" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048569" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <autoFilter ref="A25:G40"/>
   <mergeCells count="4">
